--- a/data/trans_camb/P19C07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 6,85</t>
+          <t>-0,94; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,99</t>
+          <t>-3,73; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,55</t>
+          <t>-3,24; 8,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,66</t>
+          <t>-2,12; 5,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 3,99</t>
+          <t>-3,19; 4,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,54</t>
+          <t>-3,84; 5,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 5,42</t>
+          <t>-0,23; 5,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 2,9</t>
+          <t>-2,45; 2,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,53</t>
+          <t>-2,56; 4,88</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 167,94</t>
+          <t>-14,18; 169,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-50,16; 71,32</t>
+          <t>-47,59; 83,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,12; 173,11</t>
+          <t>-49,49; 196,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-23,78; 104,4</t>
+          <t>-24,75; 106,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 73,41</t>
+          <t>-35,5; 76,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-44,67; 118,76</t>
+          <t>-47,1; 103,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 107,62</t>
+          <t>-4,11; 98,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 59,17</t>
+          <t>-32,05; 52,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-35,91; 82,87</t>
+          <t>-36,89; 94,28</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,09</t>
+          <t>-1,98; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 2,23</t>
+          <t>-2,58; 2,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,56</t>
+          <t>-1,81; 4,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 4,68</t>
+          <t>-1,09; 4,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,34</t>
+          <t>-1,13; 4,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 6,57</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 3,0</t>
+          <t>-0,72; 3,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,43</t>
+          <t>-1,19; 2,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 4,78</t>
+          <t>-0,08; 4,69</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,56; 108,34</t>
+          <t>-38,18; 109,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-49,56; 78,98</t>
+          <t>-52,11; 82,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-36,14; 149,52</t>
+          <t>-37,01; 176,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-25,51; 171,92</t>
+          <t>-21,13; 157,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 148,56</t>
+          <t>-23,33; 165,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 226,96</t>
+          <t>-0,19; 236,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 93,79</t>
+          <t>-16,87; 93,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,87; 79,49</t>
+          <t>-25,14; 82,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 152,65</t>
+          <t>1,08; 149,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,37</t>
+          <t>-1,27; 2,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,31</t>
+          <t>-0,69; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,48</t>
+          <t>-0,56; 3,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,39</t>
+          <t>-1,41; 2,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,57</t>
+          <t>-2,16; 1,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,44</t>
+          <t>-0,63; 3,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,93</t>
+          <t>-0,75; 1,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 1,75</t>
+          <t>-0,81; 1,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,03; 2,86</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,11; 181,21</t>
+          <t>-44,31; 183,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 230,08</t>
+          <t>-27,41; 271,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 244,15</t>
+          <t>-23,93; 272,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,31; 125,26</t>
+          <t>-40,53; 123,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 92,88</t>
+          <t>-59,0; 94,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 185,66</t>
+          <t>-21,01; 183,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 110,52</t>
+          <t>-24,21; 103,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,31; 95,12</t>
+          <t>-26,29; 110,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,1; 159,42</t>
+          <t>-5,02; 154,46</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 0,47</t>
+          <t>-4,26; 0,5</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 0,34</t>
+          <t>-4,48; 0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 0,76</t>
+          <t>-4,47; 0,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,7</t>
+          <t>-2,21; 1,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 2,74</t>
+          <t>-1,45; 2,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,6</t>
+          <t>-1,03; 2,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,59</t>
+          <t>-2,45; 0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,0</t>
+          <t>-2,13; 0,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,22</t>
+          <t>-2,32; 1,1</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 32,94</t>
+          <t>-79,52; 26,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-81,53; 28,14</t>
+          <t>-83,1; 19,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 28,88</t>
+          <t>-76,93; 21,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-67,34; 143,47</t>
+          <t>-65,81; 163,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,08; 208,93</t>
+          <t>-45,17; 176,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 195,08</t>
+          <t>-29,3; 217,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-66,01; 30,15</t>
+          <t>-64,31; 36,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 55,85</t>
+          <t>-54,41; 52,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 51,73</t>
+          <t>-53,28; 52,88</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 1,92</t>
+          <t>-2,11; 1,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 2,16</t>
+          <t>-1,77; 2,05</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,41</t>
+          <t>-1,97; 1,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,98</t>
+          <t>-3,03; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 1,9</t>
+          <t>-2,37; 1,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 2,36</t>
+          <t>-1,36; 2,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,87</t>
+          <t>-1,87; 0,83</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,28</t>
+          <t>-1,37; 1,42</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,42</t>
+          <t>-1,12; 1,47</t>
         </is>
       </c>
     </row>
@@ -1652,42 +1652,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,62; 570,45</t>
+          <t>-79,45; 553,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-73,4; 328,53</t>
+          <t>-79,25; 318,78</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-85,76; 156,67</t>
+          <t>-85,72; 155,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,77; 242,86</t>
+          <t>-75,87; 229,55</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-43,75; 305,02</t>
+          <t>-42,23; 320,94</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-75,75; 135,91</t>
+          <t>-75,55; 92,23</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 126,35</t>
+          <t>-56,86; 136,36</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-43,54; 155,16</t>
+          <t>-41,01; 159,86</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -1,4</t>
+          <t>-6,96; -1,13</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,12</t>
+          <t>-6,29; 0,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 0,68</t>
+          <t>-5,2; 0,64</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,01</t>
+          <t>-4,25; 0,96</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 2,15</t>
+          <t>-4,07; 1,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 0,25</t>
+          <t>-4,98; 0,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,6</t>
+          <t>-4,56; -0,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 0,38</t>
+          <t>-4,08; 0,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; -0,09</t>
+          <t>-4,15; -0,18</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -13,68</t>
+          <t>-100,0; -15,67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-91,71; 20,71</t>
+          <t>-92,51; 14,9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-78,32; 34,36</t>
+          <t>-76,78; 34,41</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,13; 77,71</t>
+          <t>-86,56; 74,58</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-78,58; 141,59</t>
+          <t>-80,88; 115,61</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-88,47; 8,76</t>
+          <t>-85,05; 23,57</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-87,98; -9,58</t>
+          <t>-87,39; -16,49</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,05; 23,29</t>
+          <t>-77,52; 25,54</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,9; -2,82</t>
+          <t>-76,61; -6,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 3,26</t>
+          <t>-3,26; 3,54</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,27</t>
+          <t>-5,09; 0,32</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 2,01</t>
+          <t>-3,18; 2,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 1,7</t>
+          <t>-3,79; 1,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 2,37</t>
+          <t>-3,35; 2,36</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,35</t>
+          <t>-2,78; 2,34</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,48</t>
+          <t>-2,6; 1,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 1,02</t>
+          <t>-2,92; 1,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 1,74</t>
+          <t>-2,27; 1,79</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>-81,18; —</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>-90,72; 261,12</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>-87,13; 380,58</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>-90,84; 315,74</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-59,02; 402,06</t>
+          <t>-58,58; 384,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-75,15; 136,01</t>
+          <t>-76,11; 158,09</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-89,45; 145,54</t>
+          <t>-89,23; 129,43</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 207,9</t>
+          <t>-57,8; 190,37</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,94</t>
+          <t>-1,13; 0,86</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,42</t>
+          <t>-1,69; 0,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,92</t>
+          <t>-1,42; 0,91</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,11</t>
+          <t>-0,83; 1,09</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,13</t>
+          <t>-0,76; 1,05</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,36</t>
+          <t>-0,72; 1,35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,75</t>
+          <t>-0,7; 0,73</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,48</t>
+          <t>-0,95; 0,52</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,88</t>
+          <t>-0,8; 0,81</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-27,19; 31,98</t>
+          <t>-28,29; 30,2</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-38,87; 15,33</t>
+          <t>-41,09; 11,97</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-34,45; 31,48</t>
+          <t>-36,79; 31,03</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 37,9</t>
+          <t>-20,56; 36,2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 38,23</t>
+          <t>-19,29; 34,3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 44,81</t>
+          <t>-18,2; 44,64</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 24,27</t>
+          <t>-18,08; 24,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 15,79</t>
+          <t>-25,08; 16,3</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-18,51; 28,23</t>
+          <t>-21,08; 26,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C07-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 6,9</t>
+          <t>-0,36; 7,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,65</t>
+          <t>-3,55; 3,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,18</t>
+          <t>-2,95; 6,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,48</t>
+          <t>-1,93; 5,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,38</t>
+          <t>-3,24; 3,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 5,66</t>
+          <t>-3,77; 5,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 5,12</t>
+          <t>-0,25; 5,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,67</t>
+          <t>-2,51; 2,58</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 4,88</t>
+          <t>-2,54; 4,6</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 169,83</t>
+          <t>-7,12; 172,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 83,58</t>
+          <t>-49,69; 75,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,49; 196,83</t>
+          <t>-41,97; 170,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,75; 106,98</t>
+          <t>-23,59; 92,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,5; 76,47</t>
+          <t>-35,72; 71,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 103,02</t>
+          <t>-45,95; 96,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 98,04</t>
+          <t>-4,72; 98,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,05; 52,65</t>
+          <t>-31,63; 50,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-36,89; 94,28</t>
+          <t>-34,69; 82,24</t>
         </is>
       </c>
     </row>
@@ -850,29 +850,29 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,62</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
           <t>1,07</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,62</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,24</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,07</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,61</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,27</t>
+          <t>2,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 3,09</t>
+          <t>-2,33; 2,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,31</t>
+          <t>-2,74; 1,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 4,87</t>
+          <t>-1,42; 4,96</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,41</t>
+          <t>-1,04; 4,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 4,36</t>
+          <t>-1,21; 4,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,81; 7,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 3,0</t>
+          <t>-0,69; 2,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 2,54</t>
+          <t>-1,19; 2,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 4,69</t>
+          <t>0,58; 5,32</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>68,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-38,18; 109,31</t>
+          <t>-45,79; 100,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 82,53</t>
+          <t>-52,88; 71,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-37,01; 176,16</t>
+          <t>-32,09; 168,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-21,13; 157,14</t>
+          <t>-22,37; 158,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 165,35</t>
+          <t>-24,13; 152,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 236,28</t>
+          <t>12,19; 263,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,87; 93,75</t>
+          <t>-15,22; 99,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 82,4</t>
+          <t>-24,13; 82,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 149,05</t>
+          <t>11,34; 168,22</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,15</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 2,29</t>
+          <t>-1,34; 2,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 3,23</t>
+          <t>-0,51; 3,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,51</t>
+          <t>-0,75; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,3</t>
+          <t>-1,47; 2,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,58</t>
+          <t>-2,08; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 3,32</t>
+          <t>-0,76; 3,13</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,89</t>
+          <t>-0,72; 1,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,98</t>
+          <t>-0,83; 1,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>-0,2; 2,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-44,31; 183,43</t>
+          <t>-51,58; 183,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 271,43</t>
+          <t>-22,85; 263,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-23,93; 272,89</t>
+          <t>-31,25; 254,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-40,53; 123,27</t>
+          <t>-41,4; 128,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,0; 94,57</t>
+          <t>-57,09; 85,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,01; 183,71</t>
+          <t>-23,05; 189,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 103,84</t>
+          <t>-24,79; 116,57</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-26,29; 110,16</t>
+          <t>-29,18; 100,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 154,46</t>
+          <t>-9,01; 137,21</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-0,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,16</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,5</t>
+          <t>-4,12; 0,62</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 0,28</t>
+          <t>-4,26; 0,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,69</t>
+          <t>-2,99; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 1,83</t>
+          <t>-2,16; 1,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,47</t>
+          <t>-1,3; 2,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 2,6</t>
+          <t>-0,6; 2,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 0,76</t>
+          <t>-2,47; 0,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,96</t>
+          <t>-2,1; 0,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,1</t>
+          <t>-1,25; 1,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-38,32%</t>
+          <t>-6,53%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-8,22%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 26,7</t>
+          <t>-77,52; 39,03</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 19,21</t>
+          <t>-83,0; 28,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-76,93; 21,22</t>
+          <t>-57,26; 85,39</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 163,03</t>
+          <t>-63,94; 148,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 176,55</t>
+          <t>-43,75; 221,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 217,08</t>
+          <t>-21,83; 199,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-64,31; 36,18</t>
+          <t>-64,07; 35,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 52,02</t>
+          <t>-55,28; 49,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,28; 52,88</t>
+          <t>-31,01; 86,56</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>-0,08</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,3</t>
+          <t>0,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 1,62</t>
+          <t>-1,9; 1,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,05</t>
+          <t>-1,76; 2,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,25</t>
+          <t>-1,91; 1,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,06</t>
+          <t>-2,83; 1,06</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,87</t>
+          <t>-2,27; 1,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,46</t>
+          <t>-1,16; 2,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,83</t>
+          <t>-1,85; 0,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,42</t>
+          <t>-1,41; 1,59</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,47</t>
+          <t>-0,99; 1,5</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,12%</t>
+          <t>-6,0%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>23,39%</t>
         </is>
       </c>
     </row>
@@ -1652,42 +1652,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,45; 553,15</t>
+          <t>-85,66; 508,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 318,78</t>
+          <t>-74,43; 389,4</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-85,72; 155,78</t>
+          <t>-82,79; 190,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 229,55</t>
+          <t>-73,47; 223,17</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-42,23; 320,94</t>
+          <t>-35,71; 258,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-75,55; 92,23</t>
+          <t>-75,04; 94,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 136,36</t>
+          <t>-58,82; 167,9</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 159,86</t>
+          <t>-38,26; 167,85</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-1,91</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-1,65</t>
+          <t>-0,83</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-1,84</t>
+          <t>-1,38</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -1,13</t>
+          <t>-6,91; -1,39</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 0,08</t>
+          <t>-6,13; -0,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 0,64</t>
+          <t>-5,15; 0,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 0,96</t>
+          <t>-4,11; 1,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,87</t>
+          <t>-3,92; 1,78</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,55</t>
+          <t>-3,84; 1,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-4,56; -0,76</t>
+          <t>-4,57; -0,65</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,3</t>
+          <t>-3,81; 0,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,18</t>
+          <t>-3,4; 0,34</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-43,37%</t>
+          <t>-45,58%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-49,43%</t>
+          <t>-24,89%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-48,07%</t>
+          <t>-35,95%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -15,67</t>
+          <t>-100,0; -19,53</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 14,9</t>
+          <t>-92,72; 23,27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-76,78; 34,41</t>
+          <t>-77,51; 30,45</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-86,56; 74,58</t>
+          <t>-84,57; 76,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,88; 115,61</t>
+          <t>-79,59; 114,03</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-85,05; 23,57</t>
+          <t>-65,9; 82,76</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-87,39; -16,49</t>
+          <t>-87,97; -16,72</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-77,52; 25,54</t>
+          <t>-75,95; 25,96</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-76,61; -6,16</t>
+          <t>-64,03; 13,42</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-0,03</t>
+          <t>-0,07</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,13</t>
+          <t>0,17</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,54</t>
+          <t>-3,5; 2,99</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 0,32</t>
+          <t>-4,94; 0,46</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,4</t>
+          <t>-3,38; 2,41</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,79; 1,49</t>
+          <t>-3,65; 1,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,36</t>
+          <t>-3,45; 2,5</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 2,34</t>
+          <t>-2,78; 2,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,48</t>
+          <t>-2,3; 1,56</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,03</t>
+          <t>-3,03; 0,97</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,79</t>
+          <t>-1,95; 1,78</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-1,32%</t>
+          <t>-3,5%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-100,0; 578,44</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-81,18; —</t>
+          <t>-82,31; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-90,72; 261,12</t>
+          <t>-88,75; 381,84</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -2104,22 +2104,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 384,89</t>
+          <t>-63,04; 338,81</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-76,11; 158,09</t>
+          <t>-70,85; 202,68</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-89,23; 129,43</t>
+          <t>-89,23; 140,17</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,8; 190,37</t>
+          <t>-53,78; 190,23</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,03</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,39</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,86</t>
+          <t>-1,05; 1,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,31</t>
+          <t>-1,54; 0,38</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,91</t>
+          <t>-0,96; 1,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,09</t>
+          <t>-0,82; 1,2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,05</t>
+          <t>-0,88; 0,95</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,35</t>
+          <t>-0,3; 1,63</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,73</t>
+          <t>-0,7; 0,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,52</t>
+          <t>-0,97; 0,45</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,81</t>
+          <t>-0,31; 1,08</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-6,68%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>11,3%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-28,29; 30,2</t>
+          <t>-26,51; 36,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 11,97</t>
+          <t>-38,13; 13,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-36,79; 31,03</t>
+          <t>-25,54; 41,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-20,56; 36,2</t>
+          <t>-20,95; 38,28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-19,29; 34,3</t>
+          <t>-22,31; 32,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,2; 44,64</t>
+          <t>-7,7; 53,97</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 24,48</t>
+          <t>-18,16; 21,51</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 16,3</t>
+          <t>-25,63; 14,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-21,08; 26,05</t>
+          <t>-8,16; 34,74</t>
         </is>
       </c>
     </row>
